--- a/src/main/resources/xlsx/security_pool_query_export_template.xlsx
+++ b/src/main/resources/xlsx/security_pool_query_export_template.xlsx
@@ -86,10 +86,10 @@
     <t>{data.maturityDate}</t>
   </si>
   <si>
-    <t>剩余期限(年)</t>
-  </si>
-  <si>
-    <t>{data.remainingTermYears}</t>
+    <t>证券期限</t>
+  </si>
+  <si>
+    <t>{data.dateExistsStr}</t>
   </si>
   <si>
     <t>证券状态</t>

--- a/src/main/resources/xlsx/security_pool_query_export_template.xlsx
+++ b/src/main/resources/xlsx/security_pool_query_export_template.xlsx
@@ -311,7 +311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.0" customWidth="true"/>
@@ -336,6 +336,7 @@
     <col min="20" max="20" width="15.0" customWidth="true"/>
     <col min="21" max="21" width="15.0" customWidth="true"/>
     <col min="22" max="22" width="15.0" customWidth="true"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
@@ -405,6 +406,9 @@
       <c r="V1" t="s" s="1">
         <v>42</v>
       </c>
+      <c r="W1" s="1" t="str">
+        <v>是否标准信用债</v>
+      </c>
     </row>
     <row r="2" ht="20.0" customHeight="true">
       <c r="A2" t="s" s="2">
@@ -473,6 +477,9 @@
       <c r="V2" t="s" s="2">
         <v>43</v>
       </c>
+      <c r="W2" s="2" t="str">
+        <v>{data.stdCreditLabel}</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q2:Q1048576">
@@ -523,6 +530,14 @@
       <formula>"否"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W1048576">
+    <cfRule type="cellIs" operator="equal" dxfId="10" priority="13">
+      <formula>"是"</formula>
+    </cfRule>
+    <cfRule type="cellIs" operator="equal" dxfId="11" priority="14">
+      <formula>"否"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>